--- a/data_karyawan.xlsx
+++ b/data_karyawan.xlsx
@@ -50,11 +50,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008B4000"/>
+        <fgColor rgb="007B3F00"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,20 +62,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,43 +454,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AE21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="8" customWidth="1" min="25" max="25"/>
     <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>NRK</t>
@@ -636,217 +648,2103 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EMP001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Tri Rahayu, AMdKep</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Perawat PT. Asama</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ICU</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>karyawan@email.com</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4904026</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>117737</v>
-      </c>
-      <c r="R2" t="n">
-        <v>58869</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>RS001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>dr. Andi Prasetyo, Sp.PD</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Dokter Spesialis Penyakit Dalam</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Poli Penyakit Dalam</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>rs001@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>370000</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>185000</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>58869</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>235474</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>249603</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>117737</v>
+      <c r="X2" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="5" t="n">
+        <v>185000</v>
+      </c>
+      <c r="AB2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="5" t="n">
+        <v>740000</v>
+      </c>
+      <c r="AD2" s="5" t="n">
+        <v>684500</v>
+      </c>
+      <c r="AE2" s="5" t="n">
+        <v>370000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EMP002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Budi Santoso</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>RS002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>dr. Siti Rahayu, Sp.OG</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Dokter Spesialis Obgyn</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Poli Kandungan</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>rs002@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>450000</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>350000</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>175000</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X3" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="5" t="n">
+        <v>175000</v>
+      </c>
+      <c r="AB3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5" t="n">
+        <v>700000</v>
+      </c>
+      <c r="AD3" s="5" t="n">
+        <v>647500</v>
+      </c>
+      <c r="AE3" s="5" t="n">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>RS003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>dr. Budi Santoso, Sp.A</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Dokter Spesialis Anak</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Poli Anak</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>rs003@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>450000</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>340000</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>170000</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X4" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="5" t="n">
+        <v>170000</v>
+      </c>
+      <c r="AB4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="5" t="n">
+        <v>680000</v>
+      </c>
+      <c r="AD4" s="5" t="n">
+        <v>629000</v>
+      </c>
+      <c r="AE4" s="5" t="n">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>RS004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>dr. Maya Indrawati</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Dokter Umum</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>rs004@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>190000</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>95000</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="5" t="n">
+        <v>95000</v>
+      </c>
+      <c r="AB5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5" t="n">
+        <v>380000</v>
+      </c>
+      <c r="AD5" s="5" t="n">
+        <v>351500</v>
+      </c>
+      <c r="AE5" s="5" t="n">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>RS005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>dr. Rizky Firmansyah</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Dokter Umum</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Poli Umum</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>budi@email.com</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="E6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>rs005@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>700000</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>176000</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>88000</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="5" t="n">
+        <v>88000</v>
+      </c>
+      <c r="AB6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="5" t="n">
+        <v>352000</v>
+      </c>
+      <c r="AD6" s="5" t="n">
+        <v>325600</v>
+      </c>
+      <c r="AE6" s="5" t="n">
+        <v>176000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>RS006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Ns. Tri Rahayu, AMdKep</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Perawat Pelaksana</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>rs006@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>4904026</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>98081</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>49040</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="5" t="n">
+        <v>49040</v>
+      </c>
+      <c r="AB7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5" t="n">
+        <v>196161</v>
+      </c>
+      <c r="AD7" s="5" t="n">
+        <v>181449</v>
+      </c>
+      <c r="AE7" s="5" t="n">
+        <v>98081</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>RS007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Ns. Dewi Kusuma, S.Kep</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Perawat Pelaksana</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>rs007@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>104000</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>52000</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="5" t="n">
+        <v>52000</v>
+      </c>
+      <c r="AB8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="5" t="n">
+        <v>208000</v>
+      </c>
+      <c r="AD8" s="5" t="n">
+        <v>192400</v>
+      </c>
+      <c r="AE8" s="5" t="n">
+        <v>104000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>RS008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Ns. Agus Hermawan, AMdKep</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Perawat Pelaksana</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>rs008@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>4904026</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>350000</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>98081</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>49040</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="5" t="n">
+        <v>49040</v>
+      </c>
+      <c r="AB9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="5" t="n">
+        <v>196161</v>
+      </c>
+      <c r="AD9" s="5" t="n">
+        <v>181449</v>
+      </c>
+      <c r="AE9" s="5" t="n">
+        <v>98081</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>RS009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Ns. Rina Marlina, S.Kep</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Perawat Pelaksana</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Rawat Inap A</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>rs009@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>102000</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>51000</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="5" t="n">
+        <v>51000</v>
+      </c>
+      <c r="AB10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="5" t="n">
+        <v>204000</v>
+      </c>
+      <c r="AD10" s="5" t="n">
+        <v>188700</v>
+      </c>
+      <c r="AE10" s="5" t="n">
+        <v>102000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>RS010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Ns. Faisal Rahman, AMdKep</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Perawat Pelaksana</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Rawat Inap B</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>rs010@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>4904026</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>98081</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>49040</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="5" t="n">
+        <v>49040</v>
+      </c>
+      <c r="AB11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="5" t="n">
+        <v>196161</v>
+      </c>
+      <c r="AD11" s="5" t="n">
+        <v>181449</v>
+      </c>
+      <c r="AE11" s="5" t="n">
+        <v>98081</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>RS011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Ns. Lestari Wulandari, S.Kep</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Perawat Senior</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>rs011@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>6500000</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L12" s="5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>130000</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>65000</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="5" t="n">
+        <v>65000</v>
+      </c>
+      <c r="AB12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="5" t="n">
+        <v>260000</v>
+      </c>
+      <c r="AD12" s="5" t="n">
+        <v>240500</v>
+      </c>
+      <c r="AE12" s="5" t="n">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>RS012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Hendra Gunawan, AMd.Rad</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Radiografer</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Radiologi</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>rs012@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>106000</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>53000</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="5" t="n">
+        <v>53000</v>
+      </c>
+      <c r="AB13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="5" t="n">
+        <v>212000</v>
+      </c>
+      <c r="AD13" s="5" t="n">
+        <v>196100</v>
+      </c>
+      <c r="AE13" s="5" t="n">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>RS013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Sari Dewi, AMd.AK</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Analis Kesehatan</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Laboratorium</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>rs013@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>102000</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>51000</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="5" t="n">
+        <v>51000</v>
+      </c>
+      <c r="AB14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="5" t="n">
+        <v>204000</v>
+      </c>
+      <c r="AD14" s="5" t="n">
+        <v>188700</v>
+      </c>
+      <c r="AE14" s="5" t="n">
+        <v>102000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>RS014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Wahyu Nugroho, AMd.Farm</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Asisten Apoteker</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Farmasi</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>rs014@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="L15" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>195000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>97500</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="M15" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>96000</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>48000</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="5" t="n">
+        <v>48000</v>
+      </c>
+      <c r="AB15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="5" t="n">
+        <v>192000</v>
+      </c>
+      <c r="AD15" s="5" t="n">
+        <v>177600</v>
+      </c>
+      <c r="AE15" s="5" t="n">
+        <v>96000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>RS015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Putri Handayani, S.Farm, Apt</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Apoteker</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Farmasi</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>rs015@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>144000</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>72000</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="5" t="n">
+        <v>72000</v>
+      </c>
+      <c r="AB16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="5" t="n">
+        <v>288000</v>
+      </c>
+      <c r="AD16" s="5" t="n">
+        <v>266400</v>
+      </c>
+      <c r="AE16" s="5" t="n">
+        <v>144000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>RS016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Ahmad Fauzi</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Staf Administrasi</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Admisi</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>rs016@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="M17" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>97500</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>390000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>416250</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>195000</v>
+      <c r="N17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>84000</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>42000</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="X17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="5" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="5" t="n">
+        <v>168000</v>
+      </c>
+      <c r="AD17" s="5" t="n">
+        <v>155400</v>
+      </c>
+      <c r="AE17" s="5" t="n">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>RS017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Yuni Astuti, SE</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Staf Keuangan</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Keuangan</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>rs017@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AB18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AD18" s="5" t="n">
+        <v>185000</v>
+      </c>
+      <c r="AE18" s="5" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>RS018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Dian Puspita, SE</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Kepala Keuangan</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Keuangan</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>rs018@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>900000</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>170000</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X19" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="AB19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="5" t="n">
+        <v>340000</v>
+      </c>
+      <c r="AD19" s="5" t="n">
+        <v>314500</v>
+      </c>
+      <c r="AE19" s="5" t="n">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>RS019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Rudi Hartono</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Staf IT</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>rs019@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>110000</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>55000</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="5" t="n">
+        <v>55000</v>
+      </c>
+      <c r="AB20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="5" t="n">
+        <v>220000</v>
+      </c>
+      <c r="AD20" s="5" t="n">
+        <v>203500</v>
+      </c>
+      <c r="AE20" s="5" t="n">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>RS020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Mega Sari, SKM</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Staf HRD</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>HRD</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>rs020@rsdelima.co.id</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>104000</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>52000</v>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="5" t="n">
+        <v>52000</v>
+      </c>
+      <c r="AB21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="5" t="n">
+        <v>208000</v>
+      </c>
+      <c r="AD21" s="5" t="n">
+        <v>192400</v>
+      </c>
+      <c r="AE21" s="5" t="n">
+        <v>104000</v>
       </c>
     </row>
   </sheetData>
